--- a/mental_health_forms/012_return_to_work_anxiety_self_assessment--mental_health_forms.xlsx
+++ b/mental_health_forms/012_return_to_work_anxiety_self_assessment--mental_health_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -914,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -1406,29 +1406,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>mindfulness</t>
+          <t>mindfulness_and_self-compassion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mindfulness</t>
+          <t>Mindfulness and self-compassion</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>return_to_work_support_needs_choices</t>
+          <t>work_environment_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>mindfulness_and_self-compassion</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mindfulness and self-compassion</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>home_office</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Home office</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>home_office</t>
+          <t>flexible_work_hours</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Home office</t>
+          <t>Flexible work hours</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>flexible_work_hours</t>
+          <t>work_from_home</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Flexible work hours</t>
+          <t>Work from home</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>work_from_home</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Work from home</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1508,29 +1508,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>on-site</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Off-site</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>work_environment_choices</t>
+          <t>work_type_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>off-site</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Off-site</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>freelance</t>
+          <t>remote</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Remote</t>
         </is>
       </c>
     </row>
@@ -1593,29 +1593,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>remote</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>work_type_choices</t>
+          <t>work_scheduling_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>on-site</t>
+          <t>fixed_hours</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Fixed hours</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>fixed_hours</t>
+          <t>variable_hours</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fixed hours</t>
+          <t>Variable hours</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>variable_hours</t>
+          <t>flexible_hours</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Variable hours</t>
+          <t>Flexible hours</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>flexible_hours</t>
+          <t>flexible_days</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Flexible hours</t>
+          <t>Flexible days</t>
         </is>
       </c>
     </row>
@@ -1678,29 +1678,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>flexible_days</t>
+          <t>flexible_weeks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Flexible days</t>
+          <t>Flexible weeks</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>work_scheduling_choices</t>
+          <t>work_location_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>flexible_weeks</t>
+          <t>office_building</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Flexible weeks</t>
+          <t>Office building</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>office_building</t>
+          <t>home_office</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Office building</t>
+          <t>Home office</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>home_office</t>
+          <t>on-site</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Home office</t>
+          <t>On-site</t>
         </is>
       </c>
     </row>
@@ -1746,29 +1746,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>on-site</t>
+          <t>off-site</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Off-site</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>work_location_choices</t>
+          <t>work_supervision_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>off-site</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Off-site</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>supervisor</t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t>Colleague</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>colleague</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Colleague</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1814,29 +1814,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>work_supervision_choices</t>
+          <t>support_team_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>manager</t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Colleague</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>colleague</t>
+          <t>mental_health_team</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Colleague</t>
+          <t>Mental Health Team</t>
         </is>
       </c>
     </row>
@@ -1899,29 +1899,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>mental_health_team</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mental Health Team</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>support_team_choices</t>
+          <t>return_to_work_anxiety_support_needed_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1933,29 +1933,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>return_to_work_anxiety_support_needed_choices</t>
+          <t>mental_health_referral_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1984,29 +1984,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>mental_health_referral_choices</t>
+          <t>return_to_work_concerns_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>undecided</t>
+          <t>work_schedule</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Undecided</t>
+          <t>Work schedule</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>work_schedule</t>
+          <t>workload</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Work schedule</t>
+          <t>Workload</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2035,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>workload</t>
+          <t>office_noise</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Workload</t>
+          <t>Office noise</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>office_noise</t>
+          <t>colleague_relationships</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Office noise</t>
+          <t>Colleague relationships</t>
         </is>
       </c>
     </row>
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>colleague_relationships</t>
+          <t>office_layout</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Colleague relationships</t>
+          <t>Office layout</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>office_layout</t>
+          <t>office_equipment</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Office layout</t>
+          <t>Office equipment</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>office_equipment</t>
+          <t>office_climate</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Office equipment</t>
+          <t>Office climate</t>
         </is>
       </c>
     </row>
@@ -2120,29 +2120,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>office_climate</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Office climate</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>return_to_work_concerns_choices</t>
+          <t>return_to_work_support_plan_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2154,27 +2154,10 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>return_to_work_support_plan_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
         <is>
           <t>False</t>
         </is>
